--- a/data/output/df_ML_models_results.xlsx
+++ b/data/output/df_ML_models_results.xlsx
@@ -473,19 +473,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x1380c0ad0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176eb8ad0&gt;</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'max_depth': 2, 'learning_rate': 0.021, 'n_estimators': 2800, 'subsample': 0.9, 'colsample_bytree': 0.98, 'gamma': 2.0, 'reg_alpha': 5.0, 'reg_lambda': 6.5, 'min_child_weight': 6}</t>
+          <t>{'max_depth': 1, 'learning_rate': 0.057, 'n_estimators': 950, 'subsample': 0.5, 'colsample_bytree': 1.0, 'gamma': 21.0, 'reg_alpha': 29.5, 'reg_lambda': 19.0, 'min_child_weight': 5}</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.46</v>
+        <v>26.01</v>
       </c>
       <c r="E2" t="n">
-        <v>1.83</v>
+        <v>21.73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -504,27 +504,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5e8d0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b56180&gt;</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.041858227295469716, 'model__l1_ratio': 0.96}</t>
+          <t>{'model__n_neighbors': 4, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 42, 'model__algorithm': 'ball_tree'}</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.69</v>
+        <v>28.31</v>
       </c>
       <c r="E3" t="n">
-        <v>23.54</v>
+        <v>31.37</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>KNeighborsRegressor</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4">
@@ -535,27 +535,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x105e7f140&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b567b0&gt;</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 600, 'max_depth': 10, 'min_samples_split': 2, 'min_samples_leaf': 5, 'max_features': None, 'bootstrap': False}</t>
+          <t>{'model__alpha': 0.041858227295469716, 'model__l1_ratio': 0.96}</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>32.71</v>
+        <v>29.24</v>
       </c>
       <c r="E4" t="n">
-        <v>9.59</v>
+        <v>23.24</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5">
@@ -566,27 +566,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5e450&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x16dafff50&gt;</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 2, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 79, 'model__algorithm': 'ball_tree'}</t>
+          <t>{'n_estimators': 600, 'max_depth': 10, 'min_samples_split': 2, 'min_samples_leaf': 5, 'max_features': None, 'bootstrap': False}</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>44</v>
+        <v>37.97</v>
       </c>
       <c r="E5" t="n">
-        <v>5.9</v>
+        <v>4.86</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -597,27 +597,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x1380634d0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dd880&gt;</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'max_depth': 5, 'learning_rate': 0.076, 'n_estimators': 100, 'subsample': 0.58, 'colsample_bytree': 0.66, 'gamma': 1.0, 'reg_alpha': 21.0, 'reg_lambda': 24.5, 'min_child_weight': 16}</t>
+          <t>{'model__alpha': 0.0005551555004438736, 'model__l1_ratio': 0.27}</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25.84</v>
+        <v>29.99</v>
       </c>
       <c r="E6" t="n">
-        <v>3.78</v>
+        <v>3.11</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7">
@@ -628,27 +628,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5f4a0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176e23ed0&gt;</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_depth': 7, 'min_samples_split': 4, 'min_samples_leaf': 12, 'max_features': None, 'bootstrap': True}</t>
+          <t>{'max_depth': 5, 'learning_rate': 0.051000000000000004, 'n_estimators': 50, 'subsample': 0.6799999999999999, 'colsample_bytree': 0.72, 'gamma': 22.5, 'reg_alpha': 29.0, 'reg_lambda': 18.5, 'min_child_weight': 5}</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>26.7</v>
+        <v>36.13</v>
       </c>
       <c r="E7" t="n">
-        <v>6.62</v>
+        <v>8.58</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -659,19 +659,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f95130&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104df1d0&gt;</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 8, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 39, 'model__algorithm': 'kd_tree'}</t>
+          <t>{'model__n_neighbors': 10, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 63, 'model__algorithm': 'kd_tree'}</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>33.83</v>
+        <v>41.98</v>
       </c>
       <c r="E8" t="n">
-        <v>5.32</v>
+        <v>7.04</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -690,27 +690,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f962a0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57f50&gt;</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'model__alpha': 148.9838559398634, 'model__l1_ratio': 0.8300000000000001}</t>
+          <t>{'n_estimators': 350, 'max_depth': 1, 'min_samples_split': 8, 'min_samples_leaf': 8, 'max_features': 'log2', 'bootstrap': True}</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>42.3</v>
+        <v>43.03</v>
       </c>
       <c r="E9" t="n">
-        <v>4.59</v>
+        <v>8.49</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -721,19 +721,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f97410&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dca70&gt;</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.0002550264850403288, 'model__l1_ratio': 0.87}</t>
+          <t>{'model__alpha': 8.117770337590418, 'model__l1_ratio': 1.0}</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>29.89</v>
+        <v>27.92</v>
       </c>
       <c r="E10" t="n">
-        <v>3.42</v>
+        <v>4.24</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -752,27 +752,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f97d10&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b574a0&gt;</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 12, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 19, 'model__algorithm': 'kd_tree'}</t>
+          <t>{'n_estimators': 250, 'max_depth': 2, 'min_samples_split': 3, 'min_samples_leaf': 14, 'max_features': None, 'bootstrap': True}</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31.36</v>
+        <v>32.53</v>
       </c>
       <c r="E11" t="n">
-        <v>10.23</v>
+        <v>5.77</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -783,27 +783,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5f260&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176e23c50&gt;</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 550, 'max_depth': 6, 'min_samples_split': 2, 'min_samples_leaf': 10, 'max_features': None, 'bootstrap': True}</t>
+          <t>{'max_depth': 3, 'learning_rate': 0.060000000000000005, 'n_estimators': 150, 'subsample': 0.8, 'colsample_bytree': 0.58, 'gamma': 2.5, 'reg_alpha': 28.5, 'reg_lambda': 29.0, 'min_child_weight': 17}</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>34.58</v>
+        <v>34.47</v>
       </c>
       <c r="E12" t="n">
-        <v>5.53</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -814,27 +814,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x138063b10&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dc3b0&gt;</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'max_depth': 1, 'learning_rate': 0.001, 'n_estimators': 2700, 'subsample': 0.58, 'colsample_bytree': 0.9199999999999999, 'gamma': 20.0, 'reg_alpha': 13.5, 'reg_lambda': 24.5, 'min_child_weight': 20}</t>
+          <t>{'model__n_neighbors': 12, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 19, 'model__algorithm': 'kd_tree'}</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>35.77</v>
+        <v>35.86</v>
       </c>
       <c r="E13" t="n">
-        <v>3.86</v>
+        <v>6.13</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>KNeighborsRegressor</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>125</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14">
@@ -845,19 +845,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f96180&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dd760&gt;</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.009349170414488468, 'model__l1_ratio': 0.08}</t>
+          <t>{'model__alpha': 0.041858227295469716, 'model__l1_ratio': 0.96}</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>38.76</v>
+        <v>53.7</v>
       </c>
       <c r="E14" t="n">
-        <v>17.16</v>
+        <v>16.47</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -876,19 +876,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5f380&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x17593e210&gt;</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 450, 'max_depth': 3, 'min_samples_split': 7, 'min_samples_leaf': 4, 'max_features': None, 'bootstrap': True}</t>
+          <t>{'n_estimators': 800, 'max_depth': 8, 'min_samples_split': 5, 'min_samples_leaf': 11, 'max_features': None, 'bootstrap': False}</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>73.69</v>
+        <v>69.39</v>
       </c>
       <c r="E15" t="n">
-        <v>31.06</v>
+        <v>22.74</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -907,19 +907,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd3b490&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b2fa80&gt;</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'max_depth': 3, 'learning_rate': 0.009000000000000001, 'n_estimators': 50, 'subsample': 0.8400000000000001, 'colsample_bytree': 0.78, 'gamma': 14.5, 'reg_alpha': 18.5, 'reg_lambda': 8.5, 'min_child_weight': 13}</t>
+          <t>{'max_depth': 4, 'learning_rate': 0.014000000000000002, 'n_estimators': 500, 'subsample': 0.56, 'colsample_bytree': 0.78, 'gamma': 22.0, 'reg_alpha': 14.0, 'reg_lambda': 25.5, 'min_child_weight': 18}</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>78.95999999999999</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>23.59</v>
+        <v>26.64</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -938,19 +938,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f97890&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104ddd00&gt;</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 23, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 59, 'model__algorithm': 'kd_tree'}</t>
+          <t>{'model__n_neighbors': 12, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 19, 'model__algorithm': 'kd_tree'}</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>80.13</v>
+        <v>76.14</v>
       </c>
       <c r="E17" t="n">
-        <v>25.9</v>
+        <v>26.41</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="18">
@@ -969,19 +969,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5f410&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57bf0&gt;</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 1000, 'max_depth': 7, 'min_samples_split': 5, 'min_samples_leaf': 3, 'max_features': None, 'bootstrap': False}</t>
+          <t>{'n_estimators': 400, 'max_depth': 10, 'min_samples_split': 8, 'min_samples_leaf': 10, 'max_features': 'sqrt', 'bootstrap': True}</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>37.38</v>
+        <v>42.19</v>
       </c>
       <c r="E18" t="n">
-        <v>10.28</v>
+        <v>20.24</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x1380ac8a0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176eccb00&gt;</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'max_depth': 4, 'learning_rate': 0.058, 'n_estimators': 50, 'subsample': 0.7, 'colsample_bytree': 0.72, 'gamma': 22.5, 'reg_alpha': 29.0, 'reg_lambda': 18.5, 'min_child_weight': 15}</t>
+          <t>{'max_depth': 3, 'learning_rate': 0.018000000000000002, 'n_estimators': 50, 'subsample': 1.0, 'colsample_bytree': 1.0, 'gamma': 19.0, 'reg_alpha': 20.5, 'reg_lambda': 2.5, 'min_child_weight': 7}</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>46.82</v>
+        <v>42.31</v>
       </c>
       <c r="E19" t="n">
-        <v>13.1</v>
+        <v>19.22</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
@@ -1031,27 +1031,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f96330&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104ddfd0&gt;</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 25, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 79, 'model__algorithm': 'kd_tree'}</t>
+          <t>{'model__alpha': 158.34134671161067, 'model__l1_ratio': 0.36}</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>49.93</v>
+        <v>46.67</v>
       </c>
       <c r="E20" t="n">
-        <v>12.65</v>
+        <v>17.14</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21">
@@ -1062,27 +1062,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f97770&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dec30&gt;</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'model__alpha': 619.5023740341801, 'model__l1_ratio': 0.47000000000000003}</t>
+          <t>{'model__n_neighbors': 2, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 79, 'model__algorithm': 'ball_tree'}</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>52.77</v>
+        <v>52.7</v>
       </c>
       <c r="E21" t="n">
-        <v>10.62</v>
+        <v>19.2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>KNeighborsRegressor</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="22">
@@ -1093,19 +1093,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x1380fa0f0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176ebcef0&gt;</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'max_depth': 1, 'learning_rate': 0.063, 'n_estimators': 3000, 'subsample': 0.62, 'colsample_bytree': 0.74, 'gamma': 26.0, 'reg_alpha': 7.0, 'reg_lambda': 10.5, 'min_child_weight': 14}</t>
+          <t>{'max_depth': 1, 'learning_rate': 0.077, 'n_estimators': 2300, 'subsample': 0.72, 'colsample_bytree': 0.8, 'gamma': 3.5, 'reg_alpha': 26.0, 'reg_lambda': 14.5, 'min_child_weight': 17}</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>34.84</v>
+        <v>41.62</v>
       </c>
       <c r="E22" t="n">
-        <v>14.82</v>
+        <v>20.02</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
@@ -1124,19 +1124,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f949e0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104df6e0&gt;</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.00015533117206750294, 'model__l1_ratio': 0.03}</t>
+          <t>{'model__alpha': 0.0002550264850403288, 'model__l1_ratio': 0.87}</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>55.22</v>
+        <v>54.68</v>
       </c>
       <c r="E23" t="n">
-        <v>28.78</v>
+        <v>29.95</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1155,27 +1155,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5ff50&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57650&gt;</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_depth': 3, 'min_samples_split': 4, 'min_samples_leaf': 3, 'max_features': None, 'bootstrap': True}</t>
+          <t>{'model__n_neighbors': 11, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 50, 'model__algorithm': 'kd_tree'}</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>64.53</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>25.77</v>
+        <v>33.13</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>KNeighborsRegressor</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>125</v>
+        <v>400</v>
       </c>
     </row>
     <row r="25">
@@ -1186,27 +1186,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f969f0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57530&gt;</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 16, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 67, 'model__algorithm': 'auto'}</t>
+          <t>{'n_estimators': 350, 'max_depth': 1, 'min_samples_split': 8, 'min_samples_leaf': 8, 'max_features': 'log2', 'bootstrap': True}</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>68.56999999999999</v>
+        <v>75.87</v>
       </c>
       <c r="E25" t="n">
-        <v>31.86</v>
+        <v>30.19</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
@@ -1217,19 +1217,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x138029040&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176df1040&gt;</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'max_depth': 3, 'learning_rate': 0.028, 'n_estimators': 2700, 'subsample': 0.52, 'colsample_bytree': 0.7, 'gamma': 10.0, 'reg_alpha': 5.0, 'reg_lambda': 27.5, 'min_child_weight': 19}</t>
+          <t>{'max_depth': 4, 'learning_rate': 0.065, 'n_estimators': 50, 'subsample': 0.86, 'colsample_bytree': 0.88, 'gamma': 19.0, 'reg_alpha': 17.5, 'reg_lambda': 12.0, 'min_child_weight': 15}</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>43.36</v>
+        <v>68.73</v>
       </c>
       <c r="E26" t="n">
-        <v>20.57</v>
+        <v>16.41</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
@@ -1248,27 +1248,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f97650&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57c80&gt;</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.041858227295469716, 'model__l1_ratio': 0.96}</t>
+          <t>{'n_estimators': 150, 'max_depth': 5, 'min_samples_split': 10, 'min_samples_leaf': 6, 'max_features': None, 'bootstrap': True}</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>47.53</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>12.22</v>
+        <v>16.15</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -1279,27 +1279,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f97c80&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dfa40&gt;</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 10, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 63, 'model__algorithm': 'kd_tree'}</t>
+          <t>{'model__alpha': 1.779466917055237, 'model__l1_ratio': 0.01}</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>50.02</v>
+        <v>70.38</v>
       </c>
       <c r="E28" t="n">
-        <v>23.55</v>
+        <v>7.63</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29">
@@ -1310,27 +1310,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5f6e0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dde20&gt;</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 600, 'max_depth': 10, 'min_samples_split': 2, 'min_samples_leaf': 5, 'max_features': None, 'bootstrap': False}</t>
+          <t>{'model__n_neighbors': 10, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 63, 'model__algorithm': 'kd_tree'}</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>50.76</v>
+        <v>71.17</v>
       </c>
       <c r="E29" t="n">
-        <v>14.53</v>
+        <v>13.22</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>KNeighborsRegressor</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>125</v>
+        <v>400</v>
       </c>
     </row>
     <row r="30">
@@ -1341,27 +1341,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f94710&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176df18c0&gt;</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.10558813779064824, 'model__l1_ratio': 0.29}</t>
+          <t>{'max_depth': 5, 'learning_rate': 0.057, 'n_estimators': 50, 'subsample': 0.6799999999999999, 'colsample_bytree': 0.72, 'gamma': 22.0, 'reg_alpha': 21.0, 'reg_lambda': 17.5, 'min_child_weight': 5}</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>20.88</v>
+        <v>22.45</v>
       </c>
       <c r="E30" t="n">
-        <v>14.66</v>
+        <v>13.83</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
@@ -1372,19 +1372,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5fad0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57ad0&gt;</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 350, 'max_depth': 8, 'min_samples_split': 3, 'min_samples_leaf': 6, 'max_features': 'log2', 'bootstrap': False}</t>
+          <t>{'n_estimators': 50, 'max_depth': 8, 'min_samples_split': 3, 'min_samples_leaf': 9, 'max_features': 'sqrt', 'bootstrap': False}</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>21.51</v>
+        <v>22.51</v>
       </c>
       <c r="E31" t="n">
-        <v>11.82</v>
+        <v>12.42</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
@@ -1403,27 +1403,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x1380298c0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dc950&gt;</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'max_depth': 1, 'learning_rate': 0.07200000000000001, 'n_estimators': 2050, 'subsample': 0.76, 'colsample_bytree': 0.54, 'gamma': 25.0, 'reg_alpha': 3.0, 'reg_lambda': 30.0, 'min_child_weight': 9}</t>
+          <t>{'model__alpha': 0.0006393711155102455, 'model__l1_ratio': 0.98}</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>22.39</v>
+        <v>22.68</v>
       </c>
       <c r="E32" t="n">
-        <v>9.380000000000001</v>
+        <v>12.14</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33">
@@ -1434,19 +1434,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f945f0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104df9b0&gt;</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 4, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 42, 'model__algorithm': 'ball_tree'}</t>
+          <t>{'model__n_neighbors': 5, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 29, 'model__algorithm': 'auto'}</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>23.2</v>
+        <v>24.14</v>
       </c>
       <c r="E33" t="n">
-        <v>9</v>
+        <v>10.59</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="34">
@@ -1465,19 +1465,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f971d0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dfbf0&gt;</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.0012363188277052211, 'model__l1_ratio': 0.15}</t>
+          <t>{'model__alpha': 0.0002550264850403288, 'model__l1_ratio': 0.87}</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>26.54</v>
+        <v>31.77</v>
       </c>
       <c r="E34" t="n">
-        <v>21.25</v>
+        <v>16.8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1496,27 +1496,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5bb50&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57e30&gt;</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'max_depth': 1, 'learning_rate': 0.08, 'n_estimators': 650, 'subsample': 0.5, 'colsample_bytree': 0.98, 'gamma': 6.0, 'reg_alpha': 17.5, 'reg_lambda': 3.0, 'min_child_weight': 11}</t>
+          <t>{'n_estimators': 950, 'max_depth': 7, 'min_samples_split': 4, 'min_samples_leaf': 12, 'max_features': None, 'bootstrap': False}</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>32.04</v>
+        <v>36.49</v>
       </c>
       <c r="E35" t="n">
-        <v>4.58</v>
+        <v>13.97</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36">
@@ -1527,27 +1527,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5fbf0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b4e950&gt;</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_depth': 8, 'min_samples_split': 4, 'min_samples_leaf': 6, 'max_features': 'sqrt', 'bootstrap': False}</t>
+          <t>{'max_depth': 3, 'learning_rate': 0.060000000000000005, 'n_estimators': 150, 'subsample': 0.8, 'colsample_bytree': 0.58, 'gamma': 2.5, 'reg_alpha': 28.5, 'reg_lambda': 29.0, 'min_child_weight': 17}</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>35.88</v>
+        <v>40.96</v>
       </c>
       <c r="E36" t="n">
-        <v>7.44</v>
+        <v>1.51</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f95be0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104decc0&gt;</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>37.92</v>
+        <v>41.34</v>
       </c>
       <c r="E37" t="n">
-        <v>18.91</v>
+        <v>16.23</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="38">
@@ -1589,19 +1589,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x13b7c00e0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dfe30&gt;</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 4, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 25, 'model__algorithm': 'auto'}</t>
+          <t>{'model__n_neighbors': 3, 'model__weights': 'distance', 'model__p': 1, 'model__leaf_size': 36, 'model__algorithm': 'ball_tree'}</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>41.05</v>
+        <v>56.57</v>
       </c>
       <c r="E38" t="n">
-        <v>12.04</v>
+        <v>56.57</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="39">
@@ -1620,27 +1620,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139208650&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57d10&gt;</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'max_depth': 1, 'learning_rate': 0.053000000000000005, 'n_estimators': 150, 'subsample': 0.6799999999999999, 'colsample_bytree': 1.0, 'gamma': 30.0, 'reg_alpha': 25.5, 'reg_lambda': 1.0, 'min_child_weight': 7}</t>
+          <t>{'n_estimators': 600, 'max_depth': 1, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': None, 'bootstrap': False}</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>45.66</v>
+        <v>57.93</v>
       </c>
       <c r="E39" t="n">
-        <v>18.5</v>
+        <v>12.65</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40">
@@ -1651,27 +1651,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5fa40&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dcc20&gt;</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 800, 'max_depth': 1, 'min_samples_split': 4, 'min_samples_leaf': 3, 'max_features': None, 'bootstrap': False}</t>
+          <t>{'model__alpha': 1.9468116557476405, 'model__l1_ratio': 0.39}</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>46.02</v>
+        <v>61.03</v>
       </c>
       <c r="E40" t="n">
-        <v>10.11</v>
+        <v>19.77</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41">
@@ -1682,27 +1682,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f96450&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x30724c950&gt;</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'model__alpha': 64.51445379907872, 'model__l1_ratio': 0.62}</t>
+          <t>{'max_depth': 1, 'learning_rate': 0.033, 'n_estimators': 50, 'subsample': 0.66, 'colsample_bytree': 0.72, 'gamma': 21.5, 'reg_alpha': 14.5, 'reg_lambda': 22.5, 'min_child_weight': 17}</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>50.67</v>
+        <v>61.2</v>
       </c>
       <c r="E41" t="n">
-        <v>15.06</v>
+        <v>17.16</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42">
@@ -1713,27 +1713,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f95760&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dfda0&gt;</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'model__alpha': 125.32145724611838, 'model__l1_ratio': 1.0}</t>
+          <t>{'model__n_neighbors': 4, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 42, 'model__algorithm': 'ball_tree'}</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>65.65000000000001</v>
+        <v>69.95</v>
       </c>
       <c r="E42" t="n">
-        <v>27.08</v>
+        <v>25.68</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>KNeighborsRegressor</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="43">
@@ -1744,19 +1744,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5f5c0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57260&gt;</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 900, 'max_depth': 4, 'min_samples_split': 2, 'min_samples_leaf': 14, 'max_features': None, 'bootstrap': False}</t>
+          <t>{'n_estimators': 550, 'max_depth': 4, 'min_samples_split': 2, 'min_samples_leaf': 12, 'max_features': None, 'bootstrap': False}</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>67.5</v>
+        <v>71.89</v>
       </c>
       <c r="E43" t="n">
-        <v>23.71</v>
+        <v>28.21</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44">
@@ -1775,27 +1775,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd53b60&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104ddeb0&gt;</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'max_depth': 2, 'learning_rate': 0.054, 'n_estimators': 50, 'subsample': 0.96, 'colsample_bytree': 0.96, 'gamma': 16.5, 'reg_alpha': 18.5, 'reg_lambda': 5.5, 'min_child_weight': 17}</t>
+          <t>{'model__alpha': 9.607488651431506, 'model__l1_ratio': 0.91}</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>74.31</v>
+        <v>72.59</v>
       </c>
       <c r="E44" t="n">
-        <v>32.93</v>
+        <v>31.45</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="45">
@@ -1806,27 +1806,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x13b7c29f0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b43c50&gt;</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 4, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 42, 'model__algorithm': 'ball_tree'}</t>
+          <t>{'max_depth': 1, 'learning_rate': 0.046, 'n_estimators': 600, 'subsample': 0.52, 'colsample_bytree': 0.78, 'gamma': 6.0, 'reg_alpha': 24.5, 'reg_lambda': 24.0, 'min_child_weight': 20}</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>75.88</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>31.04</v>
+        <v>37.25</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x138464320&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176f10410&gt;</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'max_depth': 5, 'learning_rate': 0.02, 'n_estimators': 1350, 'subsample': 0.54, 'colsample_bytree': 0.8, 'gamma': 1.0, 'reg_alpha': 14.5, 'reg_lambda': 16.0, 'min_child_weight': 19}</t>
+          <t>{'max_depth': 4, 'learning_rate': 0.075, 'n_estimators': 150, 'subsample': 0.66, 'colsample_bytree': 0.8, 'gamma': 7.0, 'reg_alpha': 21.5, 'reg_lambda': 13.0, 'min_child_weight': 19}</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>24.81</v>
+        <v>24.01</v>
       </c>
       <c r="E46" t="n">
-        <v>12.56</v>
+        <v>7.27</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47">
@@ -1868,19 +1868,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f95f40&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104ddc70&gt;</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'model__alpha': 1.6136341713591302, 'model__l1_ratio': 0.71}</t>
+          <t>{'model__alpha': 0.041858227295469716, 'model__l1_ratio': 0.96}</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>29.44</v>
+        <v>24.83</v>
       </c>
       <c r="E47" t="n">
-        <v>3.14</v>
+        <v>4.28</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1899,27 +1899,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5f530&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104de9f0&gt;</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_depth': 2, 'min_samples_split': 6, 'min_samples_leaf': 11, 'max_features': None, 'bootstrap': True}</t>
+          <t>{'model__n_neighbors': 19, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 84, 'model__algorithm': 'auto'}</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>30.18</v>
+        <v>27.4</v>
       </c>
       <c r="E48" t="n">
-        <v>2.3</v>
+        <v>6.34</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>KNeighborsRegressor</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>125</v>
+        <v>400</v>
       </c>
     </row>
     <row r="49">
@@ -1930,27 +1930,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x13b7c0440&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b572f0&gt;</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 15, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 61, 'model__algorithm': 'ball_tree'}</t>
+          <t>{'n_estimators': 700, 'max_depth': 4, 'min_samples_split': 6, 'min_samples_leaf': 10, 'max_features': 'log2', 'bootstrap': True}</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>31.71</v>
+        <v>28.22</v>
       </c>
       <c r="E49" t="n">
-        <v>4.37</v>
+        <v>4.69</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50">
@@ -1961,19 +1961,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f96690&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dd5b0&gt;</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.0003585298072319365, 'model__l1_ratio': 1.0}</t>
+          <t>{'model__alpha': 0.00011482217479097196, 'model__l1_ratio': 1.0}</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>55.34</v>
+        <v>53.09</v>
       </c>
       <c r="E50" t="n">
-        <v>14.06</v>
+        <v>16.05</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1992,27 +1992,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x1380a2190&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57da0&gt;</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'max_depth': 1, 'learning_rate': 0.083, 'n_estimators': 650, 'subsample': 0.98, 'colsample_bytree': 0.72, 'gamma': 16.5, 'reg_alpha': 17.0, 'reg_lambda': 1.0, 'min_child_weight': 11}</t>
+          <t>{'n_estimators': 900, 'max_depth': 5, 'min_samples_split': 3, 'min_samples_leaf': 8, 'max_features': None, 'bootstrap': False}</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>63.2</v>
+        <v>56.23</v>
       </c>
       <c r="E51" t="n">
-        <v>30.33</v>
+        <v>15.04</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52">
@@ -2023,27 +2023,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fb3f0b0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176e92270&gt;</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'n_estimators': 550, 'max_depth': 1, 'min_samples_split': 4, 'min_samples_leaf': 4, 'max_features': None, 'bootstrap': False}</t>
+          <t>{'max_depth': 2, 'learning_rate': 0.096, 'n_estimators': 2200, 'subsample': 0.8, 'colsample_bytree': 0.58, 'gamma': 5.5, 'reg_alpha': 2.5, 'reg_lambda': 26.5, 'min_child_weight': 14}</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>71.23999999999999</v>
+        <v>56.63</v>
       </c>
       <c r="E52" t="n">
-        <v>14.29</v>
+        <v>49.5</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53">
@@ -2054,19 +2054,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x13b7c0830&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3119ea840&gt;</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 5, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 53, 'model__algorithm': 'auto'}</t>
+          <t>{'model__n_neighbors': 2, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 6, 'model__algorithm': 'ball_tree'}</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>71.97</v>
+        <v>65.27</v>
       </c>
       <c r="E53" t="n">
-        <v>22.04</v>
+        <v>31.58</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="54">
@@ -2085,19 +2085,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x1380a2970&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176e92a50&gt;</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'max_depth': 1, 'learning_rate': 0.017, 'n_estimators': 2650, 'subsample': 0.98, 'colsample_bytree': 0.74, 'gamma': 13.5, 'reg_alpha': 9.0, 'reg_lambda': 3.5, 'min_child_weight': 6}</t>
+          <t>{'max_depth': 1, 'learning_rate': 0.098, 'n_estimators': 100, 'subsample': 0.96, 'colsample_bytree': 0.86, 'gamma': 24.0, 'reg_alpha': 12.5, 'reg_lambda': 17.5, 'min_child_weight': 5}</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>27.62</v>
+        <v>34.12</v>
       </c>
       <c r="E54" t="n">
-        <v>4.12</v>
+        <v>4.79</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55">
@@ -2116,19 +2116,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f94ef0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104de570&gt;</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.0002550264850403288, 'model__l1_ratio': 0.87}</t>
+          <t>{'model__alpha': 0.01389051456143578, 'model__l1_ratio': 0.45}</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>29.84</v>
+        <v>34.65</v>
       </c>
       <c r="E55" t="n">
-        <v>4.15</v>
+        <v>1.7</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2147,19 +2147,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x13b7c0680&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3119eba40&gt;</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 4, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 42, 'model__algorithm': 'ball_tree'}</t>
+          <t>{'model__n_neighbors': 10, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 63, 'model__algorithm': 'kd_tree'}</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>32.65</v>
+        <v>38.53</v>
       </c>
       <c r="E56" t="n">
-        <v>4.49</v>
+        <v>1.08</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="57">
@@ -2178,19 +2178,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5fda0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57410&gt;</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'max_depth': 6, 'min_samples_split': 3, 'min_samples_leaf': 9, 'max_features': 'sqrt', 'bootstrap': True}</t>
+          <t>{'n_estimators': 650, 'max_depth': 4, 'min_samples_split': 2, 'min_samples_leaf': 7, 'max_features': 'log2', 'bootstrap': True}</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>39.72</v>
+        <v>41.26</v>
       </c>
       <c r="E57" t="n">
-        <v>3.69</v>
+        <v>3.39</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58">
@@ -2209,27 +2209,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x13b7c1f40&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dc8c0&gt;</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 5, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 29, 'model__algorithm': 'auto'}</t>
+          <t>{'model__alpha': 0.4477261164915934, 'model__l1_ratio': 0.36}</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>31.92</v>
+        <v>33.58</v>
       </c>
       <c r="E58" t="n">
-        <v>18.31</v>
+        <v>15.08</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="59">
@@ -2240,27 +2240,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f96b10&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3119e88c0&gt;</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.000139345022513376, 'model__l1_ratio': 0.97}</t>
+          <t>{'model__n_neighbors': 8, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 58, 'model__algorithm': 'auto'}</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>32.38</v>
+        <v>35.51</v>
       </c>
       <c r="E59" t="n">
-        <v>16.84</v>
+        <v>14.13</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>KNeighborsRegressor</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="60">
@@ -2271,27 +2271,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5f890&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3073ce750&gt;</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'n_estimators': 700, 'max_depth': 8, 'min_samples_split': 3, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'bootstrap': False}</t>
+          <t>{'max_depth': 1, 'learning_rate': 0.037000000000000005, 'n_estimators': 1250, 'subsample': 0.88, 'colsample_bytree': 0.86, 'gamma': 9.5, 'reg_alpha': 13.0, 'reg_lambda': 11.0, 'min_child_weight': 12}</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>35.13</v>
+        <v>37.88</v>
       </c>
       <c r="E60" t="n">
-        <v>9.789999999999999</v>
+        <v>4.88</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61">
@@ -2302,27 +2302,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x1397064e0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b579b0&gt;</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'max_depth': 1, 'learning_rate': 0.065, 'n_estimators': 500, 'subsample': 0.86, 'colsample_bytree': 0.8200000000000001, 'gamma': 19.0, 'reg_alpha': 22.0, 'reg_lambda': 1.0, 'min_child_weight': 16}</t>
+          <t>{'n_estimators': 50, 'max_depth': 6, 'min_samples_split': 7, 'min_samples_leaf': 11, 'max_features': None, 'bootstrap': False}</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>36.48</v>
+        <v>41.77</v>
       </c>
       <c r="E61" t="n">
-        <v>4.59</v>
+        <v>4.43</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62">
@@ -2333,27 +2333,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5fb60&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104de180&gt;</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'max_depth': 7, 'min_samples_split': 3, 'min_samples_leaf': 15, 'max_features': None, 'bootstrap': False}</t>
+          <t>{'model__alpha': 0.041858227295469716, 'model__l1_ratio': 0.96}</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>24.83</v>
+        <v>33.15</v>
       </c>
       <c r="E62" t="n">
-        <v>11.49</v>
+        <v>5.21</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="63">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x13806ed50&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176e3b050&gt;</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'max_depth': 1, 'learning_rate': 0.066, 'n_estimators': 150, 'subsample': 0.76, 'colsample_bytree': 0.96, 'gamma': 23.5, 'reg_alpha': 28.5, 'reg_lambda': 4.5, 'min_child_weight': 15}</t>
+          <t>{'max_depth': 5, 'learning_rate': 0.023, 'n_estimators': 50, 'subsample': 0.64, 'colsample_bytree': 0.8, 'gamma': 23.0, 'reg_alpha': 27.0, 'reg_lambda': 4.0, 'min_child_weight': 13}</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>27.82</v>
+        <v>38.92</v>
       </c>
       <c r="E63" t="n">
-        <v>7.88</v>
+        <v>9.34</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64">
@@ -2395,27 +2395,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f95d00&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dff50&gt;</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'model__alpha': 1.8449632796470226, 'model__l1_ratio': 1.0}</t>
+          <t>{'model__n_neighbors': 25, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 23, 'model__algorithm': 'auto'}</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>28.93</v>
+        <v>40.18</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>10.92</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>KNeighborsRegressor</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="65">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f97ec0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57380&gt;</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 19, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 84, 'model__algorithm': 'auto'}</t>
+          <t>{'n_estimators': 150, 'max_depth': 1, 'min_samples_split': 7, 'min_samples_leaf': 8, 'max_features': 'sqrt', 'bootstrap': True}</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>30.04</v>
+        <v>41.12</v>
       </c>
       <c r="E65" t="n">
-        <v>12.24</v>
+        <v>7.13</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66">
@@ -2457,27 +2457,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f97800&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57b60&gt;</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'model__alpha': 309.9764189324157, 'model__l1_ratio': 1.0}</t>
+          <t>{'n_estimators': 500, 'max_depth': 6, 'min_samples_split': 9, 'min_samples_leaf': 15, 'max_features': None, 'bootstrap': False}</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>35.43</v>
+        <v>27.31</v>
       </c>
       <c r="E66" t="n">
-        <v>9.640000000000001</v>
+        <v>5.41</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67">
@@ -2488,27 +2488,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5fc80&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104df530&gt;</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'n_estimators': 750, 'max_depth': 3, 'min_samples_split': 2, 'min_samples_leaf': 14, 'max_features': None, 'bootstrap': False}</t>
+          <t>{'model__alpha': 2.491941804013474, 'model__l1_ratio': 0.93}</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>39.48</v>
+        <v>34.84</v>
       </c>
       <c r="E67" t="n">
-        <v>8.859999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="68">
@@ -2519,19 +2519,19 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x13806f350&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176e3b350&gt;</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'max_depth': 2, 'learning_rate': 0.001, 'n_estimators': 400, 'subsample': 0.66, 'colsample_bytree': 0.72, 'gamma': 1.0, 'reg_alpha': 27.5, 'reg_lambda': 6.0, 'min_child_weight': 14}</t>
+          <t>{'max_depth': 3, 'learning_rate': 0.003, 'n_estimators': 2800, 'subsample': 1.0, 'colsample_bytree': 0.7, 'gamma': 14.0, 'reg_alpha': 26.0, 'reg_lambda': 12.0, 'min_child_weight': 12}</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>47.56</v>
+        <v>35.53</v>
       </c>
       <c r="E68" t="n">
-        <v>6.72</v>
+        <v>15.15</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69">
@@ -2550,19 +2550,19 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f97e30&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dc290&gt;</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 25, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 29, 'model__algorithm': 'auto'}</t>
+          <t>{'model__n_neighbors': 25, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 100, 'model__algorithm': 'auto'}</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>49.19</v>
+        <v>43.31</v>
       </c>
       <c r="E69" t="n">
-        <v>12.09</v>
+        <v>8.76</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="70">
@@ -2581,19 +2581,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f97a40&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dd400&gt;</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'model__alpha': 1.6136341713591302, 'model__l1_ratio': 0.71}</t>
+          <t>{'model__alpha': 1.568513385619359, 'model__l1_ratio': 0.65}</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>38.47</v>
+        <v>31.31</v>
       </c>
       <c r="E70" t="n">
-        <v>2.37</v>
+        <v>7.57</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2612,27 +2612,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5f770&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3075dba10&gt;</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'max_depth': 3, 'min_samples_split': 7, 'min_samples_leaf': 13, 'max_features': None, 'bootstrap': False}</t>
+          <t>{'max_depth': 2, 'learning_rate': 0.003, 'n_estimators': 2200, 'subsample': 0.62, 'colsample_bytree': 0.62, 'gamma': 7.5, 'reg_alpha': 4.0, 'reg_lambda': 28.0, 'min_child_weight': 10}</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>41.36</v>
+        <v>37.52</v>
       </c>
       <c r="E71" t="n">
-        <v>2.54</v>
+        <v>4.95</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72">
@@ -2643,27 +2643,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f951c0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b575c0&gt;</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 19, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 84, 'model__algorithm': 'auto'}</t>
+          <t>{'n_estimators': 150, 'max_depth': 5, 'min_samples_split': 4, 'min_samples_leaf': 15, 'max_features': 'sqrt', 'bootstrap': False}</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>42.9</v>
+        <v>39.4</v>
       </c>
       <c r="E72" t="n">
-        <v>2.67</v>
+        <v>4.2</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73">
@@ -2674,27 +2674,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x13993b8b0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dfec0&gt;</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'max_depth': 1, 'learning_rate': 0.078, 'n_estimators': 50, 'subsample': 1.0, 'colsample_bytree': 0.5, 'gamma': 30.0, 'reg_alpha': 24.5, 'reg_lambda': 30.0, 'min_child_weight': 6}</t>
+          <t>{'model__n_neighbors': 12, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 19, 'model__algorithm': 'kd_tree'}</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>43.35</v>
+        <v>40.96</v>
       </c>
       <c r="E73" t="n">
-        <v>2.34</v>
+        <v>2.78</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>KNeighborsRegressor</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>125</v>
+        <v>400</v>
       </c>
     </row>
     <row r="74">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f94a70&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104de3c0&gt;</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>27.46</v>
+        <v>29.96</v>
       </c>
       <c r="E74" t="n">
-        <v>16.67</v>
+        <v>14.47</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2736,27 +2736,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x1399afc20&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57890&gt;</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'max_depth': 1, 'learning_rate': 0.009000000000000001, 'n_estimators': 2650, 'subsample': 0.7, 'colsample_bytree': 0.56, 'gamma': 30.0, 'reg_alpha': 2.0, 'reg_lambda': 19.0, 'min_child_weight': 14}</t>
+          <t>{'n_estimators': 450, 'max_depth': 3, 'min_samples_split': 7, 'min_samples_leaf': 4, 'max_features': None, 'bootstrap': True}</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>35.78</v>
+        <v>38.01</v>
       </c>
       <c r="E75" t="n">
-        <v>6.64</v>
+        <v>8.42</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="76">
@@ -2767,27 +2767,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5fec0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x306d08c00&gt;</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'max_depth': 3, 'min_samples_split': 3, 'min_samples_leaf': 6, 'max_features': None, 'bootstrap': True}</t>
+          <t>{'max_depth': 1, 'learning_rate': 0.001, 'n_estimators': 950, 'subsample': 0.98, 'colsample_bytree': 0.78, 'gamma': 19.0, 'reg_alpha': 1.0, 'reg_lambda': 19.0, 'min_child_weight': 5}</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>35.99</v>
+        <v>44.8</v>
       </c>
       <c r="E76" t="n">
-        <v>9.84</v>
+        <v>5.79</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="77">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f97da0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3119e84d0&gt;</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>38.67</v>
+        <v>46.66</v>
       </c>
       <c r="E77" t="n">
-        <v>12.72</v>
+        <v>6.4</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="78">
@@ -2829,19 +2829,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f963c0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dd370&gt;</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.000139345022513376, 'model__l1_ratio': 0.97}</t>
+          <t>{'model__alpha': 1.6136341713591302, 'model__l1_ratio': 0.71}</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>20.62</v>
+        <v>27.24</v>
       </c>
       <c r="E78" t="n">
-        <v>10.68</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2860,27 +2860,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x13809e5d0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3119eaba0&gt;</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'max_depth': 2, 'learning_rate': 0.016, 'n_estimators': 750, 'subsample': 1.0, 'colsample_bytree': 0.72, 'gamma': 22.0, 'reg_alpha': 8.0, 'reg_lambda': 17.0, 'min_child_weight': 5}</t>
+          <t>{'model__n_neighbors': 7, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 25, 'model__algorithm': 'kd_tree'}</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>25.53</v>
+        <v>28.04</v>
       </c>
       <c r="E79" t="n">
-        <v>9.039999999999999</v>
+        <v>10.26</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>KNeighborsRegressor</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>125</v>
+        <v>400</v>
       </c>
     </row>
     <row r="80">
@@ -2891,27 +2891,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5f650&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176f0be30&gt;</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_depth': 5, 'min_samples_split': 4, 'min_samples_leaf': 6, 'max_features': 'log2', 'bootstrap': True}</t>
+          <t>{'max_depth': 3, 'learning_rate': 0.022000000000000002, 'n_estimators': 100, 'subsample': 0.9, 'colsample_bytree': 0.72, 'gamma': 1.0, 'reg_alpha': 16.5, 'reg_lambda': 15.0, 'min_child_weight': 13}</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>28.49</v>
+        <v>29.03</v>
       </c>
       <c r="E80" t="n">
-        <v>6.96</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81">
@@ -2922,27 +2922,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f97f50&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57a40&gt;</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 25, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 46, 'model__algorithm': 'ball_tree'}</t>
+          <t>{'n_estimators': 50, 'max_depth': 2, 'min_samples_split': 5, 'min_samples_leaf': 13, 'max_features': 'log2', 'bootstrap': False}</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>30.35</v>
+        <v>30.5</v>
       </c>
       <c r="E81" t="n">
-        <v>8.32</v>
+        <v>6.3</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="82">
@@ -2953,27 +2953,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5fd10&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104ddf40&gt;</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_depth': 9, 'min_samples_split': 4, 'min_samples_leaf': 5, 'max_features': 'sqrt', 'bootstrap': True}</t>
+          <t>{'model__alpha': 0.000139345022513376, 'model__l1_ratio': 0.97}</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>18.1</v>
+        <v>22.9</v>
       </c>
       <c r="E82" t="n">
-        <v>8.859999999999999</v>
+        <v>4.88</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="83">
@@ -2984,27 +2984,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f956d0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176f09310&gt;</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.0053042909346234695, 'model__l1_ratio': 0.42}</t>
+          <t>{'max_depth': 4, 'learning_rate': 0.034, 'n_estimators': 200, 'subsample': 0.66, 'colsample_bytree': 0.66, 'gamma': 22.5, 'reg_alpha': 19.5, 'reg_lambda': 27.0, 'min_child_weight': 12}</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>20.12</v>
+        <v>24.03</v>
       </c>
       <c r="E83" t="n">
-        <v>7.2</v>
+        <v>4.86</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84">
@@ -3015,27 +3015,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x1384dbbb0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57ec0&gt;</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'max_depth': 4, 'learning_rate': 0.017, 'n_estimators': 650, 'subsample': 0.5, 'colsample_bytree': 0.72, 'gamma': 20.5, 'reg_alpha': 18.5, 'reg_lambda': 13.5, 'min_child_weight': 15}</t>
+          <t>{'n_estimators': 1000, 'max_depth': 9, 'min_samples_split': 10, 'min_samples_leaf': 7, 'max_features': None, 'bootstrap': True}</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>20.57</v>
+        <v>24.15</v>
       </c>
       <c r="E84" t="n">
-        <v>6.02</v>
+        <v>4.17</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="85">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f95370&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3119eae70&gt;</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>23.07</v>
+        <v>26.4</v>
       </c>
       <c r="E85" t="n">
-        <v>11.07</v>
+        <v>7.93</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="86">
@@ -3077,27 +3077,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5ec30&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104df380&gt;</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'max_depth': 3, 'learning_rate': 0.095, 'n_estimators': 1900, 'subsample': 0.6799999999999999, 'colsample_bytree': 0.8400000000000001, 'gamma': 23.5, 'reg_alpha': 14.5, 'reg_lambda': 23.5, 'min_child_weight': 8}</t>
+          <t>{'model__alpha': 0.041858227295469716, 'model__l1_ratio': 0.96}</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>16.14</v>
+        <v>21.69</v>
       </c>
       <c r="E86" t="n">
-        <v>11.97</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="87">
@@ -3108,27 +3108,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f94170&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b56a80&gt;</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.0012363188277052211, 'model__l1_ratio': 0.15}</t>
+          <t>{'max_depth': 1, 'learning_rate': 0.019000000000000003, 'n_estimators': 2550, 'subsample': 0.5, 'colsample_bytree': 0.8200000000000001, 'gamma': 29.5, 'reg_alpha': 7.5, 'reg_lambda': 1.5, 'min_child_weight': 16}</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>18.6</v>
+        <v>24.99</v>
       </c>
       <c r="E87" t="n">
-        <v>11.67</v>
+        <v>9.41</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="88">
@@ -3139,19 +3139,19 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5f9b0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dc4d0&gt;</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 400, 'max_depth': 3, 'min_samples_split': 6, 'min_samples_leaf': 4, 'max_features': None, 'bootstrap': True}</t>
+          <t>{'n_estimators': 250, 'max_depth': 1, 'min_samples_split': 3, 'min_samples_leaf': 10, 'max_features': None, 'bootstrap': False}</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>19.1</v>
+        <v>26.11</v>
       </c>
       <c r="E88" t="n">
-        <v>15.65</v>
+        <v>10.08</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89">
@@ -3170,19 +3170,19 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f97b60&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dd250&gt;</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 2, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 79, 'model__algorithm': 'ball_tree'}</t>
+          <t>{'model__n_neighbors': 5, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 29, 'model__algorithm': 'auto'}</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>25.43</v>
+        <v>26.4</v>
       </c>
       <c r="E89" t="n">
-        <v>12</v>
+        <v>9.32</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="90">
@@ -3201,19 +3201,19 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f952e0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dc050&gt;</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.00011293569666047012, 'model__l1_ratio': 0.98}</t>
+          <t>{'model__alpha': 0.000139345022513376, 'model__l1_ratio': 0.97}</t>
         </is>
       </c>
       <c r="D90" t="n">
         <v>25.8</v>
       </c>
       <c r="E90" t="n">
-        <v>4.81</v>
+        <v>5.04</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3232,19 +3232,19 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5f920&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dcb00&gt;</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'n_estimators': 600, 'max_depth': 2, 'min_samples_split': 10, 'min_samples_leaf': 9, 'max_features': None, 'bootstrap': True}</t>
+          <t>{'n_estimators': 400, 'max_depth': 3, 'min_samples_split': 6, 'min_samples_leaf': 4, 'max_features': None, 'bootstrap': True}</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>34.11</v>
+        <v>35.54</v>
       </c>
       <c r="E91" t="n">
-        <v>12.23</v>
+        <v>10.66</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92">
@@ -3263,27 +3263,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5f140&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104de690&gt;</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'max_depth': 1, 'learning_rate': 0.001, 'n_estimators': 1500, 'subsample': 0.9, 'colsample_bytree': 0.54, 'gamma': 25.0, 'reg_alpha': 10.0, 'reg_lambda': 12.5, 'min_child_weight': 8}</t>
+          <t>{'model__n_neighbors': 5, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 29, 'model__algorithm': 'auto'}</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>36.25</v>
+        <v>40.15</v>
       </c>
       <c r="E92" t="n">
-        <v>12.78</v>
+        <v>2.47</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>KNeighborsRegressor</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>125</v>
+        <v>400</v>
       </c>
     </row>
     <row r="93">
@@ -3294,27 +3294,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f943b0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b570b0&gt;</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 5, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 29, 'model__algorithm': 'auto'}</t>
+          <t>{'max_depth': 1, 'learning_rate': 0.001, 'n_estimators': 950, 'subsample': 0.98, 'colsample_bytree': 0.78, 'gamma': 19.0, 'reg_alpha': 1.0, 'reg_lambda': 19.0, 'min_child_weight': 5}</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>39.84</v>
+        <v>41.45</v>
       </c>
       <c r="E93" t="n">
-        <v>2.4</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94">
@@ -3325,27 +3325,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f97140&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b56e70&gt;</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 550, 'max_depth': 6, 'min_samples_split': 2, 'min_samples_leaf': 10, 'max_features': None, 'bootstrap': True}</t>
+          <t>{'max_depth': 1, 'learning_rate': 0.069, 'n_estimators': 600, 'subsample': 0.94, 'colsample_bytree': 0.8200000000000001, 'gamma': 20.0, 'reg_alpha': 4.0, 'reg_lambda': 19.0, 'min_child_weight': 15}</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>46.23</v>
+        <v>44.58</v>
       </c>
       <c r="E94" t="n">
-        <v>14.7</v>
+        <v>16.23</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95">
@@ -3356,27 +3356,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5e9f0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57920&gt;</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{'max_depth': 1, 'learning_rate': 0.002, 'n_estimators': 900, 'subsample': 0.98, 'colsample_bytree': 0.78, 'gamma': 19.0, 'reg_alpha': 1.0, 'reg_lambda': 17.5, 'min_child_weight': 5}</t>
+          <t>{'n_estimators': 750, 'max_depth': 1, 'min_samples_split': 10, 'min_samples_leaf': 13, 'max_features': 'sqrt', 'bootstrap': False}</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>47.11</v>
+        <v>53.04</v>
       </c>
       <c r="E95" t="n">
-        <v>8.050000000000001</v>
+        <v>11.72</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96">
@@ -3387,19 +3387,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x13b7c1760&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104ddb50&gt;</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 29, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 54, 'model__algorithm': 'auto'}</t>
+          <t>{'model__n_neighbors': 29, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 80, 'model__algorithm': 'ball_tree'}</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>48.09</v>
+        <v>54.25</v>
       </c>
       <c r="E96" t="n">
-        <v>6.71</v>
+        <v>13.18</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="97">
@@ -3418,19 +3418,19 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f96f00&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dede0&gt;</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{'model__alpha': 744.9271069389815, 'model__l1_ratio': 0.39}</t>
+          <t>{'model__alpha': 612.0117715317909, 'model__l1_ratio': 0.01}</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>50.64</v>
+        <v>54.31</v>
       </c>
       <c r="E97" t="n">
-        <v>4.75</v>
+        <v>8.69</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3449,27 +3449,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f967b0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104de2a0&gt;</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{'model__alpha': 233.75241321673985, 'model__l1_ratio': 1.0}</t>
+          <t>{'model__n_neighbors': 3, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 18, 'model__algorithm': 'kd_tree'}</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>72.02</v>
+        <v>49.97</v>
       </c>
       <c r="E98" t="n">
-        <v>12.98</v>
+        <v>16.9</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>KNeighborsRegressor</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="99">
@@ -3480,19 +3480,19 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5f0b0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b56f90&gt;</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{'max_depth': 1, 'learning_rate': 0.005, 'n_estimators': 800, 'subsample': 0.94, 'colsample_bytree': 0.88, 'gamma': 18.0, 'reg_alpha': 23.0, 'reg_lambda': 2.5, 'min_child_weight': 19}</t>
+          <t>{'max_depth': 1, 'learning_rate': 0.043000000000000003, 'n_estimators': 1500, 'subsample': 0.88, 'colsample_bytree': 1.0, 'gamma': 26.0, 'reg_alpha': 21.0, 'reg_lambda': 2.0, 'min_child_weight': 6}</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>86.88</v>
+        <v>54.98</v>
       </c>
       <c r="E99" t="n">
-        <v>32.18</v>
+        <v>19.65</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="100">
@@ -3511,27 +3511,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x13b7c0560&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57770&gt;</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 6, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 29, 'model__algorithm': 'auto'}</t>
+          <t>{'n_estimators': 450, 'max_depth': 3, 'min_samples_split': 7, 'min_samples_leaf': 4, 'max_features': None, 'bootstrap': True}</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>88.31</v>
+        <v>56.33</v>
       </c>
       <c r="E100" t="n">
-        <v>33.69</v>
+        <v>20.51</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101">
@@ -3542,27 +3542,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f94050&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104df260&gt;</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 1000, 'max_depth': 1, 'min_samples_split': 10, 'min_samples_leaf': 15, 'max_features': 'sqrt', 'bootstrap': False}</t>
+          <t>{'model__alpha': 13.30324510152289, 'model__l1_ratio': 0.6}</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>91.59999999999999</v>
+        <v>60.88</v>
       </c>
       <c r="E101" t="n">
-        <v>31.96</v>
+        <v>20.45</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="102">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f970b0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104dfad0&gt;</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f94440&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57800&gt;</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3624,7 +3624,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104">
@@ -3635,27 +3635,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x12fd5ea80&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x3104df650&gt;</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{'max_depth': 2, 'learning_rate': 0.065, 'n_estimators': 1300, 'subsample': 1.0, 'colsample_bytree': 0.86, 'gamma': 21.0, 'reg_alpha': 17.0, 'reg_lambda': 14.0, 'min_child_weight': 7}</t>
+          <t>{'model__n_neighbors': 22, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 96, 'model__algorithm': 'kd_tree'}</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>59.79</v>
+        <v>68.42</v>
       </c>
       <c r="E104" t="n">
-        <v>41.27</v>
+        <v>15.22</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>KNeighborsRegressor</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>125</v>
+        <v>400</v>
       </c>
     </row>
     <row r="105">
@@ -3666,27 +3666,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>&lt;optuna.study.study.Study object at 0x139f95fd0&gt;</t>
+          <t>&lt;optuna.study.study.Study object at 0x176b57020&gt;</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 22, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 96, 'model__algorithm': 'kd_tree'}</t>
+          <t>{'max_depth': 1, 'learning_rate': 0.001, 'n_estimators': 950, 'subsample': 0.98, 'colsample_bytree': 0.78, 'gamma': 19.0, 'reg_alpha': 1.0, 'reg_lambda': 19.0, 'min_child_weight': 5}</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>68.42</v>
+        <v>71.5</v>
       </c>
       <c r="E105" t="n">
-        <v>15.22</v>
+        <v>18.59</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
